--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_01-12-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_01-12-2025.xlsx
@@ -568,7 +568,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>£9.78</t>
+          <t>£9.69</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -588,7 +588,30 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>£15.52</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6642da235
+	0x7ff664032630
+	0x7ff663dc16dd
+	0x7ff663e1a27e
+	0x7ff663e1a58c
+	0x7ff663e6ed77
+	0x7ff663e6baba
+	0x7ff663e0b0ed
+	0x7ff663e0bf63
+	0x7ff664305d60
+	0x7ff6642ffe8a
+	0x7ff664321005
+	0x7ff66404d71e
+	0x7ff664054e1f
+	0x7ff66403b7c4
+	0x7ff66403b97f
+	0x7ff6640218e8
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -685,7 +708,30 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>£18.20</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6642da235
+	0x7ff664032630
+	0x7ff663dc16dd
+	0x7ff663e1a27e
+	0x7ff663e1a58c
+	0x7ff663e6ed77
+	0x7ff663e6baba
+	0x7ff663e0b0ed
+	0x7ff663e0bf63
+	0x7ff664305d60
+	0x7ff6642ffe8a
+	0x7ff664321005
+	0x7ff66404d71e
+	0x7ff664054e1f
+	0x7ff66403b7c4
+	0x7ff66403b97f
+	0x7ff6640218e8
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -732,17 +778,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>£14.08</t>
+          <t>£14.00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>£14.08</t>
+          <t>£14.00</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>£14.08</t>
+          <t>£14.00</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -782,7 +828,30 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>£21.50</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6642da235
+	0x7ff664032630
+	0x7ff663dc16dd
+	0x7ff663e1a27e
+	0x7ff663e1a58c
+	0x7ff663e6ed77
+	0x7ff663e6baba
+	0x7ff663e0b0ed
+	0x7ff663e0bf63
+	0x7ff664305d60
+	0x7ff6642ffe8a
+	0x7ff664321005
+	0x7ff66404d71e
+	0x7ff664054e1f
+	0x7ff66403b7c4
+	0x7ff66403b97f
+	0x7ff6640218e8
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -829,17 +898,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>£14.57</t>
+          <t>£14.55</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>£14.57</t>
+          <t>£14.55</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>£14.57</t>
+          <t>£14.55</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -879,7 +948,30 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>£22.89</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6642da235
+	0x7ff664032630
+	0x7ff663dc16dd
+	0x7ff663e1a27e
+	0x7ff663e1a58c
+	0x7ff663e6ed77
+	0x7ff663e6baba
+	0x7ff663e0b0ed
+	0x7ff663e0bf63
+	0x7ff664305d60
+	0x7ff6642ffe8a
+	0x7ff664321005
+	0x7ff66404d71e
+	0x7ff664054e1f
+	0x7ff66403b7c4
+	0x7ff66403b97f
+	0x7ff6640218e8
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -926,17 +1018,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>£18.18</t>
+          <t>£18.15</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>£18.18</t>
+          <t>£18.15</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>£18.18</t>
+          <t>£18.15</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -956,7 +1048,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>£18.31</t>
+          <t>£18.04</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -976,7 +1068,30 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>£26.90</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6642da235
+	0x7ff664032630
+	0x7ff663dc16dd
+	0x7ff663e1a27e
+	0x7ff663e1a58c
+	0x7ff663e6ed77
+	0x7ff663e6baba
+	0x7ff663e0b0ed
+	0x7ff663e0bf63
+	0x7ff664305d60
+	0x7ff6642ffe8a
+	0x7ff664321005
+	0x7ff66404d71e
+	0x7ff664054e1f
+	0x7ff66403b7c4
+	0x7ff66403b97f
+	0x7ff6640218e8
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1053,7 +1168,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>£20.42</t>
+          <t>£20.13</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1073,7 +1188,30 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>£33.11</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6642da235
+	0x7ff664032630
+	0x7ff663dc16dd
+	0x7ff663e1a27e
+	0x7ff663e1a58c
+	0x7ff663e6ed77
+	0x7ff663e6baba
+	0x7ff663e0b0ed
+	0x7ff663e0bf63
+	0x7ff664305d60
+	0x7ff6642ffe8a
+	0x7ff664321005
+	0x7ff66404d71e
+	0x7ff664054e1f
+	0x7ff66403b7c4
+	0x7ff66403b97f
+	0x7ff6640218e8
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1120,17 +1258,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>£20.32</t>
+          <t>£20.13</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>£20.32</t>
+          <t>£20.13</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>£20.32</t>
+          <t>£20.13</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1170,7 +1308,30 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>£34.47</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6642da235
+	0x7ff664032630
+	0x7ff663dc16dd
+	0x7ff663e1a27e
+	0x7ff663e1a58c
+	0x7ff663e6ed77
+	0x7ff663e6baba
+	0x7ff663e0b0ed
+	0x7ff663e0bf63
+	0x7ff664305d60
+	0x7ff6642ffe8a
+	0x7ff664321005
+	0x7ff66404d71e
+	0x7ff664054e1f
+	0x7ff66403b7c4
+	0x7ff66403b97f
+	0x7ff6640218e8
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1217,17 +1378,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>£23.42</t>
+          <t>£23.35</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>£23.42</t>
+          <t>£23.35</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>£23.42</t>
+          <t>£23.35</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1267,7 +1428,30 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>£35.94</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6642da235
+	0x7ff664032630
+	0x7ff663dc16dd
+	0x7ff663e1a27e
+	0x7ff663e1a58c
+	0x7ff663e6ed77
+	0x7ff663e6baba
+	0x7ff663e0b0ed
+	0x7ff663e0bf63
+	0x7ff664305d60
+	0x7ff6642ffe8a
+	0x7ff664321005
+	0x7ff66404d71e
+	0x7ff664054e1f
+	0x7ff66403b7c4
+	0x7ff66403b97f
+	0x7ff6640218e8
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1314,34 +1498,34 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>£25.40</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>£25.40</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>£25.40</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>£25.75</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>£25.49</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
           <t>£25.45</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>£25.45</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>£25.45</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>£25.75</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>£25.49</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>£25.45</t>
-        </is>
-      </c>
       <c r="I10" t="inlineStr">
         <is>
           <t>£25.44</t>
@@ -1364,7 +1548,30 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>£39.16</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6642da235
+	0x7ff664032630
+	0x7ff663dc16dd
+	0x7ff663e1a27e
+	0x7ff663e1a58c
+	0x7ff663e6ed77
+	0x7ff663e6baba
+	0x7ff663e0b0ed
+	0x7ff663e0bf63
+	0x7ff664305d60
+	0x7ff6642ffe8a
+	0x7ff664321005
+	0x7ff66404d71e
+	0x7ff664054e1f
+	0x7ff66403b7c4
+	0x7ff66403b97f
+	0x7ff6640218e8
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1461,7 +1668,30 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>£41.36</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6642da235
+	0x7ff664032630
+	0x7ff663dc16dd
+	0x7ff663e1a27e
+	0x7ff663e1a58c
+	0x7ff663e6ed77
+	0x7ff663e6baba
+	0x7ff663e0b0ed
+	0x7ff663e0bf63
+	0x7ff664305d60
+	0x7ff6642ffe8a
+	0x7ff664321005
+	0x7ff66404d71e
+	0x7ff664054e1f
+	0x7ff66403b7c4
+	0x7ff66403b97f
+	0x7ff6640218e8
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1558,7 +1788,30 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>£50.37</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6642da235
+	0x7ff664032630
+	0x7ff663dc16dd
+	0x7ff663e1a27e
+	0x7ff663e1a58c
+	0x7ff663e6ed77
+	0x7ff663e6baba
+	0x7ff663e0b0ed
+	0x7ff663e0bf63
+	0x7ff664305d60
+	0x7ff6642ffe8a
+	0x7ff664321005
+	0x7ff66404d71e
+	0x7ff664054e1f
+	0x7ff66403b7c4
+	0x7ff66403b97f
+	0x7ff6640218e8
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1655,7 +1908,30 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>£50.30</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6642da235
+	0x7ff664032630
+	0x7ff663dc16dd
+	0x7ff663e1a27e
+	0x7ff663e1a58c
+	0x7ff663e6ed77
+	0x7ff663e6baba
+	0x7ff663e0b0ed
+	0x7ff663e0bf63
+	0x7ff664305d60
+	0x7ff6642ffe8a
+	0x7ff664321005
+	0x7ff66404d71e
+	0x7ff664054e1f
+	0x7ff66403b7c4
+	0x7ff66403b97f
+	0x7ff6640218e8
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1752,7 +2028,30 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>£58.68</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6642da235
+	0x7ff664032630
+	0x7ff663dc16dd
+	0x7ff663e1a27e
+	0x7ff663e1a58c
+	0x7ff663e6ed77
+	0x7ff663e6baba
+	0x7ff663e0b0ed
+	0x7ff663e0bf63
+	0x7ff664305d60
+	0x7ff6642ffe8a
+	0x7ff664321005
+	0x7ff66404d71e
+	0x7ff664054e1f
+	0x7ff66403b7c4
+	0x7ff66403b97f
+	0x7ff6640218e8
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1829,7 +2128,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>£38.13</t>
+          <t>£37.59</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1849,7 +2148,30 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>£62.87</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6642da235
+	0x7ff664032630
+	0x7ff663dc16dd
+	0x7ff663e1a27e
+	0x7ff663e1a58c
+	0x7ff663e6ed77
+	0x7ff663e6baba
+	0x7ff663e0b0ed
+	0x7ff663e0bf63
+	0x7ff664305d60
+	0x7ff6642ffe8a
+	0x7ff664321005
+	0x7ff66404d71e
+	0x7ff664054e1f
+	0x7ff66403b7c4
+	0x7ff66403b97f
+	0x7ff6640218e8
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1896,17 +2218,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>£37.65</t>
+          <t>£37.50</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>£37.65</t>
+          <t>£37.50</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>£37.65</t>
+          <t>£37.50</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1946,7 +2268,30 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>£59.49</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6642da235
+	0x7ff664032630
+	0x7ff663dc16dd
+	0x7ff663e1a27e
+	0x7ff663e1a58c
+	0x7ff663e6ed77
+	0x7ff663e6baba
+	0x7ff663e0b0ed
+	0x7ff663e0bf63
+	0x7ff664305d60
+	0x7ff6642ffe8a
+	0x7ff664321005
+	0x7ff66404d71e
+	0x7ff664054e1f
+	0x7ff66403b7c4
+	0x7ff66403b97f
+	0x7ff6640218e8
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2140,7 +2485,30 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>£1,141.98</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6642da235
+	0x7ff664032630
+	0x7ff663dc16dd
+	0x7ff663e1a27e
+	0x7ff663e1a58c
+	0x7ff663e6ed77
+	0x7ff663e6baba
+	0x7ff663e0b0ed
+	0x7ff663e0bf63
+	0x7ff664305d60
+	0x7ff6642ffe8a
+	0x7ff664321005
+	0x7ff66404d71e
+	0x7ff664054e1f
+	0x7ff66403b7c4
+	0x7ff66403b97f
+	0x7ff6640218e8
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2237,7 +2605,30 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>£34.56</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6642da235
+	0x7ff664032630
+	0x7ff663dc16dd
+	0x7ff663e1a27e
+	0x7ff663e1a58c
+	0x7ff663e6ed77
+	0x7ff663e6baba
+	0x7ff663e0b0ed
+	0x7ff663e0bf63
+	0x7ff664305d60
+	0x7ff6642ffe8a
+	0x7ff664321005
+	0x7ff66404d71e
+	0x7ff664054e1f
+	0x7ff66403b7c4
+	0x7ff66403b97f
+	0x7ff6640218e8
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2334,7 +2725,30 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>£41.09</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6642da235
+	0x7ff664032630
+	0x7ff663dc16dd
+	0x7ff663e1a27e
+	0x7ff663e1a58c
+	0x7ff663e6ed77
+	0x7ff663e6baba
+	0x7ff663e0b0ed
+	0x7ff663e0bf63
+	0x7ff664305d60
+	0x7ff6642ffe8a
+	0x7ff664321005
+	0x7ff66404d71e
+	0x7ff664054e1f
+	0x7ff66403b7c4
+	0x7ff66403b97f
+	0x7ff6640218e8
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2431,7 +2845,30 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>£48.75</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6642da235
+	0x7ff664032630
+	0x7ff663dc16dd
+	0x7ff663e1a27e
+	0x7ff663e1a58c
+	0x7ff663e6ed77
+	0x7ff663e6baba
+	0x7ff663e0b0ed
+	0x7ff663e0bf63
+	0x7ff664305d60
+	0x7ff6642ffe8a
+	0x7ff664321005
+	0x7ff66404d71e
+	0x7ff664054e1f
+	0x7ff66403b7c4
+	0x7ff66403b97f
+	0x7ff6640218e8
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2528,7 +2965,30 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>£53.63</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6642da235
+	0x7ff664032630
+	0x7ff663dc16dd
+	0x7ff663e1a27e
+	0x7ff663e1a58c
+	0x7ff663e6ed77
+	0x7ff663e6baba
+	0x7ff663e0b0ed
+	0x7ff663e0bf63
+	0x7ff664305d60
+	0x7ff6642ffe8a
+	0x7ff664321005
+	0x7ff66404d71e
+	0x7ff664054e1f
+	0x7ff66403b7c4
+	0x7ff66403b97f
+	0x7ff6640218e8
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2625,7 +3085,30 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>£65.53</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6642da235
+	0x7ff664032630
+	0x7ff663dc16dd
+	0x7ff663e1a27e
+	0x7ff663e1a58c
+	0x7ff663e6ed77
+	0x7ff663e6baba
+	0x7ff663e0b0ed
+	0x7ff663e0bf63
+	0x7ff664305d60
+	0x7ff6642ffe8a
+	0x7ff664321005
+	0x7ff66404d71e
+	0x7ff664054e1f
+	0x7ff66403b7c4
+	0x7ff66403b97f
+	0x7ff6640218e8
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2722,7 +3205,30 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>£66.65</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6642da235
+	0x7ff664032630
+	0x7ff663dc16dd
+	0x7ff663e1a27e
+	0x7ff663e1a58c
+	0x7ff663e6ed77
+	0x7ff663e6baba
+	0x7ff663e0b0ed
+	0x7ff663e0bf63
+	0x7ff664305d60
+	0x7ff6642ffe8a
+	0x7ff664321005
+	0x7ff66404d71e
+	0x7ff664054e1f
+	0x7ff66403b7c4
+	0x7ff66403b97f
+	0x7ff6640218e8
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2819,7 +3325,30 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>£1191.68</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6642da235
+	0x7ff664032630
+	0x7ff663dc16dd
+	0x7ff663e1a27e
+	0x7ff663e1a58c
+	0x7ff663e6ed77
+	0x7ff663e6baba
+	0x7ff663e0b0ed
+	0x7ff663e0bf63
+	0x7ff664305d60
+	0x7ff6642ffe8a
+	0x7ff664321005
+	0x7ff66404d71e
+	0x7ff664054e1f
+	0x7ff66403b7c4
+	0x7ff66403b97f
+	0x7ff6640218e8
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2916,7 +3445,30 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>£66.18</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6642da235
+	0x7ff664032630
+	0x7ff663dc16dd
+	0x7ff663e1a27e
+	0x7ff663e1a58c
+	0x7ff663e6ed77
+	0x7ff663e6baba
+	0x7ff663e0b0ed
+	0x7ff663e0bf63
+	0x7ff664305d60
+	0x7ff6642ffe8a
+	0x7ff664321005
+	0x7ff66404d71e
+	0x7ff664054e1f
+	0x7ff66403b7c4
+	0x7ff66403b97f
+	0x7ff6640218e8
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
